--- a/data/trans_orig/P19C01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C01-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129286</t>
+          <t>129467</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165677</t>
+          <t>166003</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>160402</t>
+          <t>160674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>197659</t>
+          <t>198316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>303024</t>
+          <t>299541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>355095</t>
+          <t>352109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193724</t>
+          <t>193398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230115</t>
+          <t>229934</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178593</t>
+          <t>177936</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>215850</t>
+          <t>215578</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>380558</t>
+          <t>383544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>432629</t>
+          <t>436112</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168100</t>
+          <t>164030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>213828</t>
+          <t>212682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187819</t>
+          <t>189116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>234323</t>
+          <t>233666</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>369550</t>
+          <t>368378</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>435651</t>
+          <t>433919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363457</t>
+          <t>364603</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409185</t>
+          <t>413255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313385</t>
+          <t>314042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359889</t>
+          <t>358592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>689342</t>
+          <t>691074</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>755443</t>
+          <t>756615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,26%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131262</t>
+          <t>129492</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>173971</t>
+          <t>171141</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>168373</t>
+          <t>168436</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>215216</t>
+          <t>215735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>311054</t>
+          <t>308870</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>372979</t>
+          <t>373190</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>328962</t>
+          <t>331792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>371671</t>
+          <t>373441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>388349</t>
+          <t>387830</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>435192</t>
+          <t>435129</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>733518</t>
+          <t>733307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>795443</t>
+          <t>797627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86827</t>
+          <t>87870</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123696</t>
+          <t>123994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108769</t>
+          <t>109276</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146988</t>
+          <t>147128</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>205200</t>
+          <t>207319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>257223</t>
+          <t>260937</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>281052</t>
+          <t>280754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317921</t>
+          <t>316878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>292197</t>
+          <t>292057</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>330416</t>
+          <t>329909</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>586710</t>
+          <t>582996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>638733</t>
+          <t>636614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57016</t>
+          <t>57077</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86754</t>
+          <t>85510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55908</t>
+          <t>55079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83950</t>
+          <t>83412</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119969</t>
+          <t>119855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161577</t>
+          <t>160901</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185595</t>
+          <t>186839</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>215333</t>
+          <t>215272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>235132</t>
+          <t>235670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>263174</t>
+          <t>264003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>429854</t>
+          <t>430530</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>471462</t>
+          <t>471576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,73%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34974</t>
+          <t>35663</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58999</t>
+          <t>58517</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37057</t>
+          <t>38552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61723</t>
+          <t>61985</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79613</t>
+          <t>79555</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114097</t>
+          <t>113083</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153766</t>
+          <t>154248</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177791</t>
+          <t>177102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184284</t>
+          <t>184022</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208950</t>
+          <t>207455</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>344675</t>
+          <t>345689</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>379159</t>
+          <t>379217</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15051</t>
+          <t>15020</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32474</t>
+          <t>32605</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23646</t>
+          <t>22811</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46088</t>
+          <t>46073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>43332</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70673</t>
+          <t>72930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94290</t>
+          <t>94159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111713</t>
+          <t>111744</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>162120</t>
+          <t>162135</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184562</t>
+          <t>185397</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>264299</t>
+          <t>262042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>292749</t>
+          <t>291640</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>692031</t>
+          <t>687407</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>776288</t>
+          <t>777003</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>813224</t>
+          <t>813931</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>914498</t>
+          <t>907265</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1528215</t>
+          <t>1525596</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1660205</t>
+          <t>1658507</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1679957</t>
+          <t>1679242</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1764214</t>
+          <t>1768838</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1825508</t>
+          <t>1832741</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1926782</t>
+          <t>1926075</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3536047</t>
+          <t>3537745</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3668037</t>
+          <t>3670656</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>150197</t>
+          <t>149947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>188749</t>
+          <t>189586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149573</t>
+          <t>151137</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>187939</t>
+          <t>189358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>313955</t>
+          <t>313681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>368134</t>
+          <t>368422</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190427</t>
+          <t>189590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228979</t>
+          <t>229229</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183052</t>
+          <t>181633</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>221418</t>
+          <t>219854</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>382032</t>
+          <t>381744</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436211</t>
+          <t>436485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>181823</t>
+          <t>180831</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>228888</t>
+          <t>230383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204280</t>
+          <t>206378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>253694</t>
+          <t>255961</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>400260</t>
+          <t>400601</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>470804</t>
+          <t>467649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,41%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368379</t>
+          <t>366884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415444</t>
+          <t>416436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>306157</t>
+          <t>303890</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>355571</t>
+          <t>353473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>686314</t>
+          <t>689469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>756858</t>
+          <t>756517</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155236</t>
+          <t>156979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202039</t>
+          <t>200814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>225590</t>
+          <t>225030</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>274883</t>
+          <t>274534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>395472</t>
+          <t>396215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>462957</t>
+          <t>461995</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>384612</t>
+          <t>385837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>431415</t>
+          <t>429672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>383573</t>
+          <t>383922</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>432866</t>
+          <t>433426</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>782150</t>
+          <t>783112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>849635</t>
+          <t>848892</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,18%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120298</t>
+          <t>122220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>164385</t>
+          <t>167037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167704</t>
+          <t>170990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>216539</t>
+          <t>216715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>303195</t>
+          <t>298575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366884</t>
+          <t>365435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>378454</t>
+          <t>375802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>422541</t>
+          <t>420619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345741</t>
+          <t>345565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>394576</t>
+          <t>391290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>738235</t>
+          <t>739684</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>801924</t>
+          <t>806544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,98%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75456</t>
+          <t>75224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110472</t>
+          <t>109328</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89129</t>
+          <t>89694</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128534</t>
+          <t>127373</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>173777</t>
+          <t>175445</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224166</t>
+          <t>224491</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250838</t>
+          <t>251982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285854</t>
+          <t>286086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>262181</t>
+          <t>263342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>301586</t>
+          <t>301021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>527859</t>
+          <t>527534</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>578248</t>
+          <t>576580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32839</t>
+          <t>32988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58448</t>
+          <t>58970</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53336</t>
+          <t>54453</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83745</t>
+          <t>83235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96206</t>
+          <t>94137</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134886</t>
+          <t>133773</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204042</t>
+          <t>203520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229651</t>
+          <t>229502</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>216844</t>
+          <t>217354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247253</t>
+          <t>246136</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>428193</t>
+          <t>429306</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466873</t>
+          <t>468942</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16062</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36709</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46271</t>
+          <t>45695</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75397</t>
+          <t>74546</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67930</t>
+          <t>68559</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102121</t>
+          <t>103058</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>148217</t>
+          <t>147791</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>168864</t>
+          <t>167661</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>227016</t>
+          <t>227867</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>256142</t>
+          <t>256718</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>385218</t>
+          <t>384281</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>419409</t>
+          <t>418780</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>803968</t>
+          <t>809706</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>910699</t>
+          <t>913371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1023560</t>
+          <t>1023692</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1132517</t>
+          <t>1131777</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1851991</t>
+          <t>1863103</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2006171</t>
+          <t>2017148</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2003960</t>
+          <t>2001288</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2110691</t>
+          <t>2104953</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2012778</t>
+          <t>2013518</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2121735</t>
+          <t>2121603</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4053782</t>
+          <t>4042805</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4207962</t>
+          <t>4196850</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>167318</t>
+          <t>168065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205584</t>
+          <t>205616</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170257</t>
+          <t>170640</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>207078</t>
+          <t>207984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>347855</t>
+          <t>347814</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>401074</t>
+          <t>403157</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,2%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>147256</t>
+          <t>147224</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185522</t>
+          <t>184775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>144852</t>
+          <t>143946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181673</t>
+          <t>181290</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>303696</t>
+          <t>301613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>356915</t>
+          <t>356956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175864</t>
+          <t>176115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>221613</t>
+          <t>220352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>200093</t>
+          <t>201421</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>243823</t>
+          <t>245046</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>387472</t>
+          <t>391643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>453277</t>
+          <t>450353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,5%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271465</t>
+          <t>272726</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>317214</t>
+          <t>316963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252897</t>
+          <t>251674</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296627</t>
+          <t>295299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>536520</t>
+          <t>539444</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>602325</t>
+          <t>598154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,43%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>203380</t>
+          <t>202913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>253066</t>
+          <t>250361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>243604</t>
+          <t>244584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>292339</t>
+          <t>292833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>466411</t>
+          <t>461594</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>532354</t>
+          <t>528232</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304794</t>
+          <t>307499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>354480</t>
+          <t>354947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>280741</t>
+          <t>280247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329476</t>
+          <t>328496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598586</t>
+          <t>602708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664529</t>
+          <t>669346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>192618</t>
+          <t>191546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>238111</t>
+          <t>238649</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>217008</t>
+          <t>213984</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>263338</t>
+          <t>261652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>420994</t>
+          <t>417970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>486940</t>
+          <t>485642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274261</t>
+          <t>273723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>319754</t>
+          <t>320826</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281546</t>
+          <t>283232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>327876</t>
+          <t>330900</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>570316</t>
+          <t>571614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>636262</t>
+          <t>639286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114563</t>
+          <t>115274</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154675</t>
+          <t>150656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134154</t>
+          <t>136201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177195</t>
+          <t>177851</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>258444</t>
+          <t>262067</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>317582</t>
+          <t>317783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>216327</t>
+          <t>220346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>256439</t>
+          <t>255728</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>218678</t>
+          <t>218022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>261719</t>
+          <t>259672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>449293</t>
+          <t>449092</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>508431</t>
+          <t>504808</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67591</t>
+          <t>68677</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97460</t>
+          <t>97346</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79702</t>
+          <t>80074</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>114149</t>
+          <t>112574</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>156347</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>199662</t>
+          <t>198868</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132665</t>
+          <t>132779</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162534</t>
+          <t>161448</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162799</t>
+          <t>164374</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>197246</t>
+          <t>196874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>307412</t>
+          <t>308206</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>351351</t>
+          <t>350727</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,17%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34550</t>
+          <t>34626</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55128</t>
+          <t>54322</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57824</t>
+          <t>58769</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89968</t>
+          <t>91097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99627</t>
+          <t>101238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138960</t>
+          <t>136424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91929</t>
+          <t>92735</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112507</t>
+          <t>112431</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137911</t>
+          <t>136782</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170055</t>
+          <t>169110</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235976</t>
+          <t>238512</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>275309</t>
+          <t>273698</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,0%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1037677</t>
+          <t>1032978</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1143813</t>
+          <t>1137089</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1191683</t>
+          <t>1193046</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1299392</t>
+          <t>1302499</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2254138</t>
+          <t>2258370</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2403527</t>
+          <t>2401253</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1520520</t>
+          <t>1527244</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1626656</t>
+          <t>1631355</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1567923</t>
+          <t>1564816</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1675632</t>
+          <t>1674269</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3128121</t>
+          <t>3130395</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3277510</t>
+          <t>3273278</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2023 (tasa de respuesta: 99,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>224799</t>
+          <t>225491</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>293858</t>
+          <t>293257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>201844</t>
+          <t>202308</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243486</t>
+          <t>241643</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>444612</t>
+          <t>444226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>523148</t>
+          <t>523616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89589</t>
+          <t>90190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>158648</t>
+          <t>157956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60055</t>
+          <t>61898</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101697</t>
+          <t>101233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163840</t>
+          <t>163372</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242376</t>
+          <t>242762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>239872</t>
+          <t>239298</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>288437</t>
+          <t>285621</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>319673</t>
+          <t>319963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>402876</t>
+          <t>408650</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>576812</t>
+          <t>574884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>686770</t>
+          <t>680678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113914</t>
+          <t>116730</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>162479</t>
+          <t>163053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96816</t>
+          <t>91042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180019</t>
+          <t>179729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>215272</t>
+          <t>221364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325230</t>
+          <t>327158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>292689</t>
+          <t>293402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>341433</t>
+          <t>339275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>315481</t>
+          <t>315069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>352185</t>
+          <t>351769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>621708</t>
+          <t>620165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>682292</t>
+          <t>682199</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,61%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>182609</t>
+          <t>184767</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>231353</t>
+          <t>230640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>179696</t>
+          <t>180112</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216400</t>
+          <t>216812</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373631</t>
+          <t>373724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>434215</t>
+          <t>435758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159011</t>
+          <t>167563</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>531575</t>
+          <t>531250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>334556</t>
+          <t>344438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>439975</t>
+          <t>440407</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>470570</t>
+          <t>462908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>947566</t>
+          <t>950973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,82%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331353</t>
+          <t>331678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>703917</t>
+          <t>695365</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>260617</t>
+          <t>260185</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366036</t>
+          <t>356154</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>615953</t>
+          <t>612546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1092949</t>
+          <t>1100611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>260964</t>
+          <t>259960</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>304080</t>
+          <t>303635</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>284610</t>
+          <t>283967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>318049</t>
+          <t>318440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>554407</t>
+          <t>555315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>610517</t>
+          <t>607915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,23%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>242499</t>
+          <t>242944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285615</t>
+          <t>286619</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>216477</t>
+          <t>216086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>249916</t>
+          <t>250559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>470588</t>
+          <t>473190</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>526698</t>
+          <t>525790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>163604</t>
+          <t>164206</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>194705</t>
+          <t>194107</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80414</t>
+          <t>83771</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>319582</t>
+          <t>319185</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>203396</t>
+          <t>200162</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>496048</t>
+          <t>497855</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,9%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164648</t>
+          <t>165246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>195749</t>
+          <t>195147</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>280327</t>
+          <t>280724</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>519495</t>
+          <t>516138</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>463214</t>
+          <t>461407</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>755866</t>
+          <t>759100</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>101685</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129098</t>
+          <t>128304</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155984</t>
+          <t>154432</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>182560</t>
+          <t>183441</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>263765</t>
+          <t>264250</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>305080</t>
+          <t>302704</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>147128</t>
+          <t>147922</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>173873</t>
+          <t>174541</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>226127</t>
+          <t>225246</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>252703</t>
+          <t>254255</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>379833</t>
+          <t>382209</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>421148</t>
+          <t>420663</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1376402</t>
+          <t>1400399</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1951046</t>
+          <t>1951534</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1585742</t>
+          <t>1587861</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2149709</t>
+          <t>2147506</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3318150</t>
+          <t>3328718</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4056925</t>
+          <t>4020537</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1403880</t>
+          <t>1403392</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1978524</t>
+          <t>1954527</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1429118</t>
+          <t>1431321</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1993085</t>
+          <t>1990966</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2876827</t>
+          <t>2913215</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3615602</t>
+          <t>3605034</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C01-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C01-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129467</t>
+          <t>127751</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166003</t>
+          <t>165529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>160674</t>
+          <t>158683</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>198316</t>
+          <t>198202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>299541</t>
+          <t>299833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>352109</t>
+          <t>354822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193398</t>
+          <t>193872</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229934</t>
+          <t>231650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177936</t>
+          <t>178050</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>215578</t>
+          <t>217569</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>383544</t>
+          <t>380831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436112</t>
+          <t>435820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164030</t>
+          <t>166613</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>212682</t>
+          <t>213578</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189116</t>
+          <t>189301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233666</t>
+          <t>232190</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>368378</t>
+          <t>372355</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>433919</t>
+          <t>434769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364603</t>
+          <t>363707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413255</t>
+          <t>410672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314042</t>
+          <t>315518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358592</t>
+          <t>358407</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691074</t>
+          <t>690224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>756615</t>
+          <t>752638</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129492</t>
+          <t>130232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>171141</t>
+          <t>172386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>168436</t>
+          <t>167808</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>215735</t>
+          <t>215500</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>308870</t>
+          <t>312267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373190</t>
+          <t>372822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>331792</t>
+          <t>330547</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>373441</t>
+          <t>372701</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>387830</t>
+          <t>388065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>435129</t>
+          <t>435757</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>733307</t>
+          <t>733675</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>797627</t>
+          <t>794230</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87870</t>
+          <t>87993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123994</t>
+          <t>124219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109276</t>
+          <t>109071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147128</t>
+          <t>147758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>207319</t>
+          <t>206069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260937</t>
+          <t>258181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>280754</t>
+          <t>280529</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>316878</t>
+          <t>316755</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>292057</t>
+          <t>291427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>329909</t>
+          <t>330114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>582996</t>
+          <t>585752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>636614</t>
+          <t>637864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57077</t>
+          <t>57151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85510</t>
+          <t>87023</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55079</t>
+          <t>56262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83412</t>
+          <t>84211</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119855</t>
+          <t>120765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160901</t>
+          <t>159654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186839</t>
+          <t>185326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>215272</t>
+          <t>215198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>235670</t>
+          <t>234871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>264003</t>
+          <t>262820</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>430530</t>
+          <t>431777</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>471576</t>
+          <t>470666</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35663</t>
+          <t>34650</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58517</t>
+          <t>59065</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38552</t>
+          <t>37742</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61985</t>
+          <t>61220</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79555</t>
+          <t>80511</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113083</t>
+          <t>113798</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154248</t>
+          <t>153700</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177102</t>
+          <t>178115</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>184022</t>
+          <t>184787</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>207455</t>
+          <t>208265</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>345689</t>
+          <t>344974</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>379217</t>
+          <t>378261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32605</t>
+          <t>32364</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>23128</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46073</t>
+          <t>47299</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43332</t>
+          <t>44175</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72930</t>
+          <t>72290</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94159</t>
+          <t>94400</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111744</t>
+          <t>111946</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>162135</t>
+          <t>160909</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>185397</t>
+          <t>185080</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>262042</t>
+          <t>262682</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>291640</t>
+          <t>290797</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>687407</t>
+          <t>687219</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>777003</t>
+          <t>780082</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>813931</t>
+          <t>812786</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>907265</t>
+          <t>908419</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1525596</t>
+          <t>1521653</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1658507</t>
+          <t>1660640</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1679242</t>
+          <t>1676163</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1768838</t>
+          <t>1769026</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1832741</t>
+          <t>1831587</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1926075</t>
+          <t>1927220</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3537745</t>
+          <t>3535612</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3670656</t>
+          <t>3674599</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,72%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149947</t>
+          <t>151220</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>189586</t>
+          <t>189758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151137</t>
+          <t>150691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>189358</t>
+          <t>188304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>313681</t>
+          <t>311694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>368422</t>
+          <t>365340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189590</t>
+          <t>189418</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229229</t>
+          <t>227956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>181633</t>
+          <t>182687</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>219854</t>
+          <t>220300</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>381744</t>
+          <t>384826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436485</t>
+          <t>438472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>180831</t>
+          <t>182995</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>230383</t>
+          <t>229122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206378</t>
+          <t>205554</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>255961</t>
+          <t>254082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>400601</t>
+          <t>399792</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>467649</t>
+          <t>470864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366884</t>
+          <t>368145</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416436</t>
+          <t>414272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303890</t>
+          <t>305769</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353473</t>
+          <t>354297</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>689469</t>
+          <t>686254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>756517</t>
+          <t>757326</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,45%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156979</t>
+          <t>155296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>200814</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>225030</t>
+          <t>224823</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>274534</t>
+          <t>276117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>396215</t>
+          <t>395095</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>461995</t>
+          <t>463810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,25%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>385837</t>
+          <t>385930</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>429672</t>
+          <t>431355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>383922</t>
+          <t>382339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>433426</t>
+          <t>433633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>783112</t>
+          <t>781297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>848892</t>
+          <t>850012</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>122220</t>
+          <t>122094</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167037</t>
+          <t>165201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>170990</t>
+          <t>166662</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>216715</t>
+          <t>216150</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>298575</t>
+          <t>303012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>365435</t>
+          <t>368293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>375802</t>
+          <t>377638</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>420619</t>
+          <t>420745</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345565</t>
+          <t>346130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>391290</t>
+          <t>395618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739684</t>
+          <t>736826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>806544</t>
+          <t>802107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75224</t>
+          <t>75229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109328</t>
+          <t>108702</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89694</t>
+          <t>91387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>127373</t>
+          <t>126873</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>175445</t>
+          <t>173993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224491</t>
+          <t>224974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>251982</t>
+          <t>252608</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>286086</t>
+          <t>286081</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>263342</t>
+          <t>263842</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>301021</t>
+          <t>299328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>527534</t>
+          <t>527051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>576580</t>
+          <t>578032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32988</t>
+          <t>32452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58970</t>
+          <t>58877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54453</t>
+          <t>55912</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83235</t>
+          <t>84859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94137</t>
+          <t>93914</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133773</t>
+          <t>132888</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>203520</t>
+          <t>203613</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229502</t>
+          <t>230038</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217354</t>
+          <t>215730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246136</t>
+          <t>244677</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>429306</t>
+          <t>430191</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>468942</t>
+          <t>469165</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17265</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37135</t>
+          <t>36580</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45695</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74546</t>
+          <t>76077</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68559</t>
+          <t>68943</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103058</t>
+          <t>101952</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>147791</t>
+          <t>148346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167661</t>
+          <t>168500</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>227867</t>
+          <t>226336</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>256718</t>
+          <t>255570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>384281</t>
+          <t>385387</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>418780</t>
+          <t>418396</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,85%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>809706</t>
+          <t>805087</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>913371</t>
+          <t>907853</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1023692</t>
+          <t>1019742</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1131777</t>
+          <t>1132844</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1863103</t>
+          <t>1864483</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2017148</t>
+          <t>2018008</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2001288</t>
+          <t>2006806</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2104953</t>
+          <t>2109572</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2013518</t>
+          <t>2012451</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2121603</t>
+          <t>2125553</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4042805</t>
+          <t>4041945</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4196850</t>
+          <t>4195470</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>168065</t>
+          <t>168225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205616</t>
+          <t>204310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170640</t>
+          <t>170987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>207984</t>
+          <t>207016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>347814</t>
+          <t>349754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>403157</t>
+          <t>403475</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,25%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>147224</t>
+          <t>148530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184775</t>
+          <t>184615</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143946</t>
+          <t>144914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181290</t>
+          <t>180943</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>301613</t>
+          <t>301295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>356956</t>
+          <t>355016</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176115</t>
+          <t>175812</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220352</t>
+          <t>218951</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>201421</t>
+          <t>201256</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>245046</t>
+          <t>243006</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>391643</t>
+          <t>389774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>450353</t>
+          <t>451356</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>272726</t>
+          <t>274127</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>316963</t>
+          <t>317266</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>251674</t>
+          <t>253714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>295299</t>
+          <t>295464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>539444</t>
+          <t>538441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>598154</t>
+          <t>600023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>202913</t>
+          <t>204187</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>250361</t>
+          <t>250088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>244584</t>
+          <t>243594</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>292833</t>
+          <t>294365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>461594</t>
+          <t>463589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>528232</t>
+          <t>528206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307499</t>
+          <t>307772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>354947</t>
+          <t>353673</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>280247</t>
+          <t>278715</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328496</t>
+          <t>329486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602708</t>
+          <t>602734</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>669346</t>
+          <t>667351</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,01%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>191546</t>
+          <t>191691</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>238649</t>
+          <t>238994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>213984</t>
+          <t>216124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>261652</t>
+          <t>262168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>417970</t>
+          <t>422068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>485642</t>
+          <t>487257</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>273723</t>
+          <t>273378</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320826</t>
+          <t>320681</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283232</t>
+          <t>282716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>330900</t>
+          <t>328760</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>571614</t>
+          <t>569999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>639286</t>
+          <t>635188</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,08%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115274</t>
+          <t>113231</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150656</t>
+          <t>152660</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136201</t>
+          <t>134527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177851</t>
+          <t>175567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>262067</t>
+          <t>261561</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>317783</t>
+          <t>316178</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>220346</t>
+          <t>218342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255728</t>
+          <t>257771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>218022</t>
+          <t>220306</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>259672</t>
+          <t>261346</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>449092</t>
+          <t>450697</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>504808</t>
+          <t>505314</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68677</t>
+          <t>67400</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97346</t>
+          <t>97292</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80074</t>
+          <t>78777</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112574</t>
+          <t>111382</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>156347</t>
+          <t>158199</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198868</t>
+          <t>200605</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132779</t>
+          <t>132833</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161448</t>
+          <t>162725</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>164374</t>
+          <t>165566</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>196874</t>
+          <t>198171</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>308206</t>
+          <t>306469</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>350727</t>
+          <t>348875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34626</t>
+          <t>35689</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54322</t>
+          <t>55098</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58769</t>
+          <t>58735</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91097</t>
+          <t>90567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101238</t>
+          <t>99908</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136424</t>
+          <t>136952</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92735</t>
+          <t>91959</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112431</t>
+          <t>111368</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136782</t>
+          <t>137312</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>169110</t>
+          <t>169144</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>238512</t>
+          <t>237984</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>273698</t>
+          <t>275028</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1032978</t>
+          <t>1035993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1137089</t>
+          <t>1135352</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1193046</t>
+          <t>1186673</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1302499</t>
+          <t>1299243</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2258370</t>
+          <t>2255915</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2401253</t>
+          <t>2411091</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1527244</t>
+          <t>1528981</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1631355</t>
+          <t>1628340</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1564816</t>
+          <t>1568072</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1674269</t>
+          <t>1680642</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3130395</t>
+          <t>3120557</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3273278</t>
+          <t>3275733</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>261780</t>
+          <t>250515</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225491</t>
+          <t>219159</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>293257</t>
+          <t>280205</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>223902</t>
+          <t>249728</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>202308</t>
+          <t>223049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241643</t>
+          <t>270248</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>485682</t>
+          <t>500243</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>444226</t>
+          <t>457484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>523616</t>
+          <t>537337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>121667</t>
+          <t>128339</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90190</t>
+          <t>98649</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157956</t>
+          <t>159695</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79639</t>
+          <t>93512</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61898</t>
+          <t>72992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101233</t>
+          <t>120191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>201306</t>
+          <t>221851</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163372</t>
+          <t>184757</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242762</t>
+          <t>264610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>263659</t>
+          <t>292609</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>239298</t>
+          <t>263531</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>285621</t>
+          <t>319958</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>352477</t>
+          <t>313392</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>319963</t>
+          <t>291265</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>408650</t>
+          <t>334205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>616136</t>
+          <t>606001</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>574884</t>
+          <t>573049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>680678</t>
+          <t>645084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>69,48%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>138692</t>
+          <t>153284</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116730</t>
+          <t>125935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163053</t>
+          <t>182362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>147215</t>
+          <t>169217</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91042</t>
+          <t>148404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179729</t>
+          <t>191344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>285906</t>
+          <t>322501</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>221364</t>
+          <t>283418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>327158</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>317136</t>
+          <t>360161</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>293402</t>
+          <t>334452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>339275</t>
+          <t>383603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>334940</t>
+          <t>383579</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>315069</t>
+          <t>363687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>351769</t>
+          <t>403280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>652076</t>
+          <t>743739</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>620165</t>
+          <t>710145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>682199</t>
+          <t>776245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>206906</t>
+          <t>240963</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184767</t>
+          <t>217521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>230640</t>
+          <t>266672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>196941</t>
+          <t>223703</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>180112</t>
+          <t>204002</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216812</t>
+          <t>243595</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>403847</t>
+          <t>464666</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373724</t>
+          <t>432160</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>435758</t>
+          <t>498260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>373589</t>
+          <t>402386</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>167563</t>
+          <t>377745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>531250</t>
+          <t>431782</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>411195</t>
+          <t>447851</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>344438</t>
+          <t>424775</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>440407</t>
+          <t>467833</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>784783</t>
+          <t>850237</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>462908</t>
+          <t>814440</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>950973</t>
+          <t>883396</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>489339</t>
+          <t>275913</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331678</t>
+          <t>246517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>695365</t>
+          <t>300554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>289397</t>
+          <t>273906</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>260185</t>
+          <t>253924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>356154</t>
+          <t>296982</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>778736</t>
+          <t>549819</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>612546</t>
+          <t>516660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1100611</t>
+          <t>585616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>281785</t>
+          <t>306109</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>259960</t>
+          <t>283606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>303635</t>
+          <t>330147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>300786</t>
+          <t>334921</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>283967</t>
+          <t>317129</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>318440</t>
+          <t>353597</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>582571</t>
+          <t>641030</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>555315</t>
+          <t>612111</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>607915</t>
+          <t>672409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>264794</t>
+          <t>287246</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>242944</t>
+          <t>263208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>286619</t>
+          <t>309749</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>233740</t>
+          <t>260928</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>216086</t>
+          <t>242252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250559</t>
+          <t>278720</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>498534</t>
+          <t>548174</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>473190</t>
+          <t>516795</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>525790</t>
+          <t>577093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,53%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>178306</t>
+          <t>199966</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>164206</t>
+          <t>182427</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>194107</t>
+          <t>215974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>205787</t>
+          <t>226231</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83771</t>
+          <t>212091</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>319185</t>
+          <t>241156</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>384093</t>
+          <t>426196</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>200162</t>
+          <t>405625</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>497855</t>
+          <t>448513</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>181047</t>
+          <t>197778</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165246</t>
+          <t>181770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>195147</t>
+          <t>215317</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>394122</t>
+          <t>202694</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>280724</t>
+          <t>187769</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>516138</t>
+          <t>216834</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>575169</t>
+          <t>400473</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461407</t>
+          <t>378156</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>759100</t>
+          <t>421044</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>114956</t>
+          <t>127585</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101685</t>
+          <t>112996</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128304</t>
+          <t>141706</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>168754</t>
+          <t>188094</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>154432</t>
+          <t>171308</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>183441</t>
+          <t>203446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>283710</t>
+          <t>315679</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>264250</t>
+          <t>294099</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>302704</t>
+          <t>337685</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>161270</t>
+          <t>175776</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>147922</t>
+          <t>161655</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174541</t>
+          <t>190365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>239933</t>
+          <t>257692</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>225246</t>
+          <t>242340</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>254255</t>
+          <t>274478</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>401203</t>
+          <t>433468</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>382209</t>
+          <t>411462</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>420663</t>
+          <t>455048</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>276226</t>
+          <t>303361</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>276226</t>
+          <t>303361</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>276226</t>
+          <t>303361</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>684913</t>
+          <t>749147</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>684913</t>
+          <t>749147</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>684913</t>
+          <t>749147</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1791211</t>
+          <t>1939330</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1400399</t>
+          <t>1872035</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1951534</t>
+          <t>2002868</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1997841</t>
+          <t>2143796</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1587861</t>
+          <t>2091003</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2147506</t>
+          <t>2197801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3789051</t>
+          <t>4083126</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3328718</t>
+          <t>3990974</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4020537</t>
+          <t>4163549</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1563715</t>
+          <t>1459299</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1403392</t>
+          <t>1395761</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1954527</t>
+          <t>1526594</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1580986</t>
+          <t>1481652</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1431321</t>
+          <t>1427647</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1990966</t>
+          <t>1534445</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3144701</t>
+          <t>2940951</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2913215</t>
+          <t>2860528</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3605034</t>
+          <t>3033103</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3354926</t>
+          <t>3398629</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3354926</t>
+          <t>3398629</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3354926</t>
+          <t>3398629</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6933752</t>
+          <t>7024077</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6933752</t>
+          <t>7024077</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6933752</t>
+          <t>7024077</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
